--- a/data/trans_orig/P05B_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P05B_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9365</t>
+          <t>9254</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24793</t>
+          <t>24559</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>7708</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23272</t>
+          <t>22377</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19486</t>
+          <t>20478</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40086</t>
+          <t>41393</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>446630</t>
+          <t>446864</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>462058</t>
+          <t>462169</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>283408</t>
+          <t>284303</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>298669</t>
+          <t>298972</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>738018</t>
+          <t>736711</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>758618</t>
+          <t>757626</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21448</t>
+          <t>20756</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7398</t>
+          <t>7008</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23528</t>
+          <t>21255</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16815</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37507</t>
+          <t>37018</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>345486</t>
+          <t>346178</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>360734</t>
+          <t>361451</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>348337</t>
+          <t>350610</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>364467</t>
+          <t>364857</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>701292</t>
+          <t>701781</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>722488</t>
+          <t>721984</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5860</t>
+          <t>6408</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18707</t>
+          <t>20183</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>5366</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17976</t>
+          <t>19134</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13927</t>
+          <t>13735</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32001</t>
+          <t>32282</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>523682</t>
+          <t>522206</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>536529</t>
+          <t>535981</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149806</t>
+          <t>148648</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162563</t>
+          <t>162416</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>678170</t>
+          <t>677889</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>696244</t>
+          <t>696436</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29794</t>
+          <t>28359</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56280</t>
+          <t>56135</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23680</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44742</t>
+          <t>44722</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58853</t>
+          <t>57687</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94169</t>
+          <t>91271</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1180288</t>
+          <t>1180433</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1206774</t>
+          <t>1208209</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>669543</t>
+          <t>669563</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>690605</t>
+          <t>691310</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1856684</t>
+          <t>1859582</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1892000</t>
+          <t>1893166</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3387</t>
+          <t>3343</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13507</t>
+          <t>13689</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19496</t>
+          <t>18826</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41085</t>
+          <t>39623</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24962</t>
+          <t>24534</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47313</t>
+          <t>48561</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>337048</t>
+          <t>336866</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>347168</t>
+          <t>347212</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>526043</t>
+          <t>527505</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>547632</t>
+          <t>548302</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>870370</t>
+          <t>869122</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>892721</t>
+          <t>893149</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4485</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18597</t>
+          <t>18809</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43904</t>
+          <t>44979</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73941</t>
+          <t>74951</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>53602</t>
+          <t>52847</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>88143</t>
+          <t>85544</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>279604</t>
+          <t>279392</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>293716</t>
+          <t>293017</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1174819</t>
+          <t>1173809</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1204856</t>
+          <t>1203781</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1458817</t>
+          <t>1461416</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1493358</t>
+          <t>1494113</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>78329</t>
+          <t>77853</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>118021</t>
+          <t>116282</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>135423</t>
+          <t>137548</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>185375</t>
+          <t>184655</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>226712</t>
+          <t>224398</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>285587</t>
+          <t>288975</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3148049</t>
+          <t>3149788</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3187741</t>
+          <t>3188217</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3191125</t>
+          <t>3191845</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3241077</t>
+          <t>3238952</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6356983</t>
+          <t>6353595</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6415858</t>
+          <t>6418172</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6821</t>
+          <t>6813</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21755</t>
+          <t>22231</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>884</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8417</t>
+          <t>7368</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8890</t>
+          <t>8651</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25482</t>
+          <t>26049</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>412587</t>
+          <t>412111</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>427521</t>
+          <t>427529</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>306037</t>
+          <t>307086</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313578</t>
+          <t>313570</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>723314</t>
+          <t>722747</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>739906</t>
+          <t>740145</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3121</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16875</t>
+          <t>17218</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>2956</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13802</t>
+          <t>14302</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8258</t>
+          <t>8184</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25695</t>
+          <t>25841</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>398693</t>
+          <t>398350</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>412447</t>
+          <t>412380</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>324209</t>
+          <t>323709</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>335026</t>
+          <t>335055</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>727884</t>
+          <t>727738</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>745321</t>
+          <t>745395</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12167</t>
+          <t>11128</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>964</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9082</t>
+          <t>8431</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>4149</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15402</t>
+          <t>15970</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>615218</t>
+          <t>616257</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>625396</t>
+          <t>625392</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>246924</t>
+          <t>247575</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>255026</t>
+          <t>255042</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>867989</t>
+          <t>867421</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>879431</t>
+          <t>879242</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12770</t>
+          <t>12924</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32022</t>
+          <t>31127</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11710</t>
+          <t>11977</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30198</t>
+          <t>30381</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27789</t>
+          <t>28053</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53103</t>
+          <t>56008</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1123967</t>
+          <t>1124862</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1143219</t>
+          <t>1143065</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>735435</t>
+          <t>735252</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>753923</t>
+          <t>753656</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1868519</t>
+          <t>1865614</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1893833</t>
+          <t>1893569</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11557</t>
+          <t>12030</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>3136</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17186</t>
+          <t>17028</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6928</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23393</t>
+          <t>22636</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>499039</t>
+          <t>498566</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>508631</t>
+          <t>508620</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>741104</t>
+          <t>741262</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>755408</t>
+          <t>755154</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1245494</t>
+          <t>1246251</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1261959</t>
+          <t>1262145</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1864</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10483</t>
+          <t>10582</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10796</t>
+          <t>10988</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28491</t>
+          <t>27542</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15381</t>
+          <t>14120</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34102</t>
+          <t>34172</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253571</t>
+          <t>253472</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262176</t>
+          <t>262190</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1072518</t>
+          <t>1073467</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1090213</t>
+          <t>1090021</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1330961</t>
+          <t>1330891</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1349682</t>
+          <t>1350943</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43128</t>
+          <t>41539</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>75620</t>
+          <t>74241</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42160</t>
+          <t>42774</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>73973</t>
+          <t>74363</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>94176</t>
+          <t>93706</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>138454</t>
+          <t>137973</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3332313</t>
+          <t>3333692</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3364805</t>
+          <t>3366394</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3459431</t>
+          <t>3459041</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3491244</t>
+          <t>3490630</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6802883</t>
+          <t>6803364</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6847161</t>
+          <t>6847631</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13608</t>
+          <t>13935</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>974</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8882</t>
+          <t>9699</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17357</t>
+          <t>17808</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>415484</t>
+          <t>415157</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>427068</t>
+          <t>427056</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>336349</t>
+          <t>335532</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>344253</t>
+          <t>344257</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>756967</t>
+          <t>756516</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>770212</t>
+          <t>770222</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9220</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3170</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15086</t>
+          <t>14788</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>4399</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16866</t>
+          <t>18435</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>367015</t>
+          <t>369757</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>357187</t>
+          <t>357485</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369103</t>
+          <t>369132</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>731642</t>
+          <t>730073</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>744452</t>
+          <t>744109</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>794</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10388</t>
+          <t>10606</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>793</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>12299</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>510442</t>
+          <t>510224</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>520035</t>
+          <t>520036</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>676919</t>
+          <t>674654</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>686165</t>
+          <t>686160</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,88%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15336</t>
+          <t>16442</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35761</t>
+          <t>35725</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13461</t>
+          <t>13363</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34496</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33889</t>
+          <t>33913</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60079</t>
+          <t>61861</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1108135</t>
+          <t>1108171</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1128560</t>
+          <t>1127454</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>787387</t>
+          <t>789866</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>808422</t>
+          <t>808520</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1905699</t>
+          <t>1903917</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1931889</t>
+          <t>1931865</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19595</t>
+          <t>18375</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7294</t>
+          <t>7592</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21921</t>
+          <t>23187</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15329</t>
+          <t>15198</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35209</t>
+          <t>34940</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>601111</t>
+          <t>602331</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>616012</t>
+          <t>615756</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>715288</t>
+          <t>714022</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>729915</t>
+          <t>729617</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1322706</t>
+          <t>1322975</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1342586</t>
+          <t>1342717</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5020</t>
+          <t>5239</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21048</t>
+          <t>19923</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42181</t>
+          <t>43083</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21034</t>
+          <t>21130</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45044</t>
+          <t>46251</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281227</t>
+          <t>281008</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1032667</t>
+          <t>1031765</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1053800</t>
+          <t>1054925</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1316051</t>
+          <t>1314844</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1340061</t>
+          <t>1339965</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34289</t>
+          <t>33601</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63364</t>
+          <t>62429</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58955</t>
+          <t>59905</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>94201</t>
+          <t>94765</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>101367</t>
+          <t>100146</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>148431</t>
+          <t>146452</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3313642</t>
+          <t>3314577</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3342717</t>
+          <t>3343405</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3423366</t>
+          <t>3422802</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3458612</t>
+          <t>3457662</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6746142</t>
+          <t>6748121</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6793206</t>
+          <t>6794427</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>10868</t>
+          <t>11171</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20224</t>
+          <t>21386</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7259</t>
+          <t>7474</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14546</t>
+          <t>15217</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>18127</t>
+          <t>18645</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10932</t>
+          <t>10872</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29356</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>492888</t>
+          <t>538011</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>483532</t>
+          <t>527796</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>498544</t>
+          <t>543721</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>437127</t>
+          <t>477673</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>429840</t>
+          <t>469930</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>441015</t>
+          <t>481433</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>930016</t>
+          <t>1015684</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>918787</t>
+          <t>1004022</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>937211</t>
+          <t>1023457</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>503756</t>
+          <t>549182</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>503756</t>
+          <t>549182</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>503756</t>
+          <t>549182</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>444386</t>
+          <t>485147</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>444386</t>
+          <t>485147</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>444386</t>
+          <t>485147</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>948143</t>
+          <t>1034329</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>948143</t>
+          <t>1034329</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>948143</t>
+          <t>1034329</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>578</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>7034</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>7271</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3553</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15047</t>
+          <t>13999</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>9647</t>
+          <t>9800</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>5098</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16887</t>
+          <t>16712</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>449198</t>
+          <t>479988</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>444359</t>
+          <t>475483</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>451028</t>
+          <t>481939</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>374907</t>
+          <t>415416</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>367097</t>
+          <t>408688</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>378591</t>
+          <t>419391</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>824105</t>
+          <t>895405</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>816865</t>
+          <t>888493</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>828924</t>
+          <t>900107</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>451608</t>
+          <t>482517</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>451608</t>
+          <t>482517</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>451608</t>
+          <t>482517</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382144</t>
+          <t>422687</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382144</t>
+          <t>422687</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382144</t>
+          <t>422687</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>833752</t>
+          <t>905205</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>833752</t>
+          <t>905205</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>833752</t>
+          <t>905205</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>4860</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12652</t>
+          <t>11442</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>428</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4418</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>6662</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14029</t>
+          <t>13062</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>663393</t>
+          <t>466752</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>655612</t>
+          <t>460170</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>667603</t>
+          <t>469823</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>164634</t>
+          <t>184640</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>161466</t>
+          <t>181857</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165720</t>
+          <t>186014</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>828027</t>
+          <t>651392</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>820119</t>
+          <t>644992</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>832512</t>
+          <t>655158</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>165884</t>
+          <t>186442</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>165884</t>
+          <t>186442</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>165884</t>
+          <t>186442</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834148</t>
+          <t>658054</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834148</t>
+          <t>658054</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834148</t>
+          <t>658054</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>4567</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18665</t>
+          <t>17779</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9599</t>
+          <t>10434</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>5920</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16631</t>
+          <t>16377</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>19571</t>
+          <t>20288</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12074</t>
+          <t>13330</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30178</t>
+          <t>30454</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1022401</t>
+          <t>1119516</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1013708</t>
+          <t>1111591</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1027618</t>
+          <t>1124803</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>967997</t>
+          <t>850230</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>960965</t>
+          <t>844287</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>973494</t>
+          <t>854744</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1990398</t>
+          <t>1969746</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1979791</t>
+          <t>1959580</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1997895</t>
+          <t>1976704</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1032373</t>
+          <t>1129370</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1032373</t>
+          <t>1129370</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1032373</t>
+          <t>1129370</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977596</t>
+          <t>860664</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977596</t>
+          <t>860664</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977596</t>
+          <t>860664</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2009969</t>
+          <t>1990034</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2009969</t>
+          <t>1990034</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2009969</t>
+          <t>1990034</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>5275</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>2366</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10631</t>
+          <t>12290</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11565</t>
+          <t>11982</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6941</t>
+          <t>7353</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18538</t>
+          <t>18478</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,22 +10075,22 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>16850</t>
+          <t>17257</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10756</t>
+          <t>11484</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25332</t>
+          <t>25059</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>469597</t>
+          <t>561035</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>464250</t>
+          <t>554020</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>472934</t>
+          <t>563944</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>828232</t>
+          <t>816698</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>821259</t>
+          <t>810202</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>832856</t>
+          <t>821327</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,27 +10188,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1297828</t>
+          <t>1377733</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1289346</t>
+          <t>1369931</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1303922</t>
+          <t>1383506</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>474881</t>
+          <t>566310</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474881</t>
+          <t>566310</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474881</t>
+          <t>566310</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>839797</t>
+          <t>828680</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>839797</t>
+          <t>828680</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>839797</t>
+          <t>828680</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1314678</t>
+          <t>1394990</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1314678</t>
+          <t>1394990</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1314678</t>
+          <t>1394990</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2473</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9469</t>
+          <t>9887</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2591</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9248</t>
+          <t>9734</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -10461,7 +10461,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>754764</t>
+          <t>837332</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>750276</t>
+          <t>832638</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>757271</t>
+          <t>840052</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>995271</t>
+          <t>1074559</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>991004</t>
+          <t>1070018</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>997912</t>
+          <t>1077161</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>759745</t>
+          <t>842525</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>759745</t>
+          <t>842525</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>759745</t>
+          <t>842525</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000252</t>
+          <t>1079752</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000252</t>
+          <t>1079752</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000252</t>
+          <t>1079752</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>33405</t>
+          <t>33689</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22536</t>
+          <t>23609</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48901</t>
+          <t>45997</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>41891</t>
+          <t>44156</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31150</t>
+          <t>34380</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54574</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>75296</t>
+          <t>77845</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59216</t>
+          <t>62563</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>96188</t>
+          <t>97433</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3337985</t>
+          <t>3402530</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3322489</t>
+          <t>3390222</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3348854</t>
+          <t>3412610</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3527661</t>
+          <t>3581989</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3514978</t>
+          <t>3568920</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3538402</t>
+          <t>3591765</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6865646</t>
+          <t>6984519</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6844754</t>
+          <t>6964931</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6881726</t>
+          <t>6999801</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3371390</t>
+          <t>3436219</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3371390</t>
+          <t>3436219</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3371390</t>
+          <t>3436219</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3569552</t>
+          <t>3626145</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3569552</t>
+          <t>3626145</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3569552</t>
+          <t>3626145</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6940942</t>
+          <t>7062364</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6940942</t>
+          <t>7062364</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6940942</t>
+          <t>7062364</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
